--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -9,6 +9,8 @@
   </bookViews>
   <sheets>
     <sheet name="データ一覧" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="規制情報の属性" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="規制情報の型" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="111">
   <si>
     <t xml:space="preserve">ファイル名</t>
   </si>
@@ -91,6 +93,9 @@
     <t xml:space="preserve">2608071600data.zip</t>
   </si>
   <si>
+    <t xml:space="preserve">規制情報のみ10:00時点</t>
+  </si>
+  <si>
     <t xml:space="preserve">〇の数</t>
   </si>
   <si>
@@ -107,6 +112,249 @@
   </si>
   <si>
     <t xml:space="preserve">作成: scripts/build_mlit_map_index.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">属性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">区分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出現時点数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/29 12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/30 08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/30 12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/30 16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/31 08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/31 16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/01 18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/02 18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/03 12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/03 16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/04 13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/04 16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/07 16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地物数（合計）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">始点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">始点住所</t>
+  </si>
+  <si>
+    <t xml:space="preserve">始点緯度経度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">市町村名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">延長_Km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">県名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終点住所</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終点緯度経度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制延長_Km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制方向</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制理由</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制種別</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制開始_内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制開始_日時</t>
+  </si>
+  <si>
+    <t xml:space="preserve">路線名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路種別</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人身_有無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">－</t>
+  </si>
+  <si>
+    <t xml:space="preserve">停電_有無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地整番号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">孤立集落_有無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">整備局名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">物損_有無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">県番号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制変更_内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制変更_日時</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迂回路_有無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">始点経度緯度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表示スタイル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_dashArray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_opacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_iconAnchor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_iconSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_iconUrl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_markerType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">セルの意味: 「全」＝その時点の全地物が持つ／数字＝持っている地物の数（赤字。持たない地物が混ざる）／「－」＝その時点には無い。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アンダースコアで始まる属性は地図の描画用（色・太さなど）で、規制の中身ではない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">属性が地物ごとに違うのは、レコードの型が混ざっているため。内訳は「規制情報の型」シート。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">レコードの型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">説明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拡張</t>
+  </si>
+  <si>
+    <t xml:space="preserve">県フォーマットに、整備局名・規制変更_日時・迂回路/孤立集落/人身/物損/停電_有無などを足したもの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">方向あり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">規制方向と規制延長_Kmを持つ。高速道路・直轄国道のレコード</t>
+  </si>
+  <si>
+    <t xml:space="preserve">区間名のみ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">始点・終点がIC名で、座標も日時も無い。高速道路のレコード</t>
+  </si>
+  <si>
+    <t xml:space="preserve">属性なし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">整理IDだけで属性が無い線（紫・半透明）。何の規制かはデータから分からない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">県フォーマット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">住所・緯度経度・規制開始_日時・延長_Kmを持つ。都道府県道/補助国道/市区町村道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ジオメトリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">線</t>
+  </si>
+  <si>
+    <t xml:space="preserve">線42＋点1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">型は属性の組み合わせで判定している（上から順に当てはめる）。道路種別の値ではないので、実際の管理者と1対1ではない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「区間名のみ」は座標も規制開始日時も持たないため、線形と期間はこのデータからは作れない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「属性なし」は整理IDだけの紫の線で、07/31〜08/01の3時点にだけ現れる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「拡張」は08/04以降にだけ現れ、迂回路・孤立集落・人身・物損・停電の有無を持つ。</t>
   </si>
 </sst>
 </file>
@@ -117,7 +365,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd\ hh:mm"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +403,40 @@
     <font>
       <sz val="9"/>
       <color rgb="FF595959"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFBFBFBF"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
       <name val="Meiryo"/>
       <family val="0"/>
       <charset val="1"/>
@@ -223,7 +505,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -260,6 +542,54 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -273,7 +603,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -773,7 +1103,7 @@
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -789,14 +1119,16 @@
       <c r="E15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" s="6" t="n">
         <f aca="false">COUNTIF(C2:C15,"〇")</f>
@@ -814,22 +1146,2489 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:P44"/>
+  <sheetFormatPr defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="4" style="0" width="5.46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="61.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K2" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="L2" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="M2" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="N2" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="O2" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="P2" s="12" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="J3" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="L3" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" s="15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="M5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="P5" s="15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="L6" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="M6" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="N6" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="O6" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="P6" s="15" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="L7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="M7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="N7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="O7" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="P7" s="15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="L8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="M8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="N8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="O8" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="P8" s="15" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="M9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="N9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="O9" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="P9" s="15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="M11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="N11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="O11" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="P11" s="15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="N12" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="O12" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="P12" s="15" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="J18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="M18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="N18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="O18" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="P18" s="15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="M19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="N19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="O19" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="P19" s="15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="J20" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N22" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N24" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N25" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N26" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N28" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N29" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N30" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N31" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="O32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P32" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P33" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J34" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="K34" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M34" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N34" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O34" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="P34" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P35" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O36" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P36" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="O37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P37" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="O38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P38" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="O39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P39" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="O40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P40" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="47.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="3" style="0" width="5.46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="61.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" s="14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="O6" s="14" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="12" t="n">
+        <f aca="false">SUM(C2:C6)</f>
+        <v>29</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <f aca="false">SUM(D2:D6)</f>
+        <v>43</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <f aca="false">SUM(E2:E6)</f>
+        <v>43</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <f aca="false">SUM(F2:F6)</f>
+        <v>43</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <f aca="false">SUM(G2:G6)</f>
+        <v>55</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <f aca="false">SUM(H2:H6)</f>
+        <v>55</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <f aca="false">SUM(I2:I6)</f>
+        <v>55</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <f aca="false">SUM(J2:J6)</f>
+        <v>44</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <f aca="false">SUM(K2:K6)</f>
+        <v>44</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <f aca="false">SUM(L2:L6)</f>
+        <v>44</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <f aca="false">SUM(M2:M6)</f>
+        <v>45</v>
+      </c>
+      <c r="N7" s="12" t="n">
+        <f aca="false">SUM(N2:N6)</f>
+        <v>45</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <f aca="false">SUM(O2:O6)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="119">
   <si>
     <t xml:space="preserve">ファイル名</t>
   </si>
@@ -300,25 +300,37 @@
     <t xml:space="preserve">レコードの型</t>
   </si>
   <si>
-    <t xml:space="preserve">説明</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拡張</t>
-  </si>
-  <si>
-    <t xml:space="preserve">県フォーマットに、整備局名・規制変更_日時・迂回路/孤立集落/人身/物損/停電_有無などを足したもの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">方向あり</t>
-  </si>
-  <si>
-    <t xml:space="preserve">規制方向と規制延長_Kmを持つ。高速道路・直轄国道のレコード</t>
+    <t xml:space="preserve">持っている属性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路種別の内訳（全時点の合計）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">災害詳細つき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">住所・座標・開始日時に加えて、地整番号・整備局名・県番号・規制変更_日時/内容・迂回路/孤立集落/人身/物損/停電_有無を持つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">補助国道 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">方向・規制延長つき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">住所・座標・開始日時に加えて、規制方向と規制延長_Kmを持つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高速道路 38、直轄国道 26</t>
   </si>
   <si>
     <t xml:space="preserve">区間名のみ</t>
   </si>
   <si>
-    <t xml:space="preserve">始点・終点がIC名で、座標も日時も無い。高速道路のレコード</t>
+    <t xml:space="preserve">始点・終点が地点名（IC名など）。住所・座標・開始日時のいずれも持たない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高速道路 79、一般国道 3</t>
   </si>
   <si>
     <t xml:space="preserve">属性なし</t>
@@ -327,10 +339,16 @@
     <t xml:space="preserve">整理IDだけで属性が無い線（紫・半透明）。何の規制かはデータから分からない</t>
   </si>
   <si>
-    <t xml:space="preserve">県フォーマット</t>
-  </si>
-  <si>
-    <t xml:space="preserve">住所・緯度経度・規制開始_日時・延長_Kmを持つ。都道府県道/補助国道/市区町村道</t>
+    <t xml:space="preserve">(値なし) 39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">住所・座標・日時</t>
+  </si>
+  <si>
+    <t xml:space="preserve">住所・緯度経度・規制開始_日時・延長_Kmを持つ、最も多い型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">都道府県道 329、補助国道 41、市区町村道 25、国道445号 1</t>
   </si>
   <si>
     <t xml:space="preserve">合計</t>
@@ -345,16 +363,22 @@
     <t xml:space="preserve">線42＋点1</t>
   </si>
   <si>
-    <t xml:space="preserve">型は属性の組み合わせで判定している（上から順に当てはめる）。道路種別の値ではないので、実際の管理者と1対1ではない。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「区間名のみ」は座標も規制開始日時も持たないため、線形と期間はこのデータからは作れない。</t>
+    <t xml:space="preserve">型の名前は「どの属性を持つか」だけで付けている。データのどこにも出所は書かれていないので、県が出したものか国が出したものかは分からない。どの道路種別が入るかも推測せず、実数をC列に出している。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">判定は上から順に当てはめる（地整番号があれば「災害詳細つき」、無くて規制方向があれば「方向・規制延長つき」…）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「区間名のみ」は座標も規制開始日時も持たないため、線形と期間はこのデータからは作れない（ジオメトリの線はあるので、地図に出すことはできる）。</t>
   </si>
   <si>
     <t xml:space="preserve">「属性なし」は整理IDだけの紫の線で、07/31〜08/01の3時点にだけ現れる。</t>
   </si>
   <si>
-    <t xml:space="preserve">「拡張」は08/04以降にだけ現れ、迂回路・孤立集落・人身・物損・停電の有無を持つ。</t>
+    <t xml:space="preserve">「災害詳細つき」は08/04以降の3件だけで、いずれも道路種別は補助国道。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道路種別の値そのものにも揺れがある（「一般国道」と「補助国道」「直轄国道」が混在、路線名が入っている1件など）。</t>
   </si>
 </sst>
 </file>
@@ -505,7 +529,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -584,6 +608,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3218,12 +3246,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="47.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="3" style="0" width="5.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="4" style="0" width="5.46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="61.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3233,55 +3262,58 @@
       <c r="B1" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>37</v>
-      </c>
       <c r="H1" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="20" t="s">
+    <row r="2" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>68</v>
+      <c r="B2" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>68</v>
@@ -3310,8 +3342,8 @@
       <c r="L2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="14" t="n">
-        <v>3</v>
+      <c r="M2" s="16" t="s">
+        <v>68</v>
       </c>
       <c r="N2" s="14" t="n">
         <v>3</v>
@@ -3319,20 +3351,23 @@
       <c r="O2" s="14" t="n">
         <v>3</v>
       </c>
+      <c r="P2" s="14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="14" t="n">
+      <c r="A3" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="14" t="n">
-        <v>5</v>
-      </c>
       <c r="E3" s="14" t="n">
         <v>5</v>
       </c>
@@ -3366,22 +3401,25 @@
       <c r="O3" s="14" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>6</v>
+      <c r="P3" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>102</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="14" t="n">
         <v>5</v>
@@ -3396,7 +3434,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" s="14" t="n">
         <v>7</v>
@@ -3405,7 +3443,7 @@
         <v>7</v>
       </c>
       <c r="M4" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N4" s="14" t="n">
         <v>8</v>
@@ -3413,16 +3451,19 @@
       <c r="O4" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="P4" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>68</v>
+      <c r="A5" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>68</v>
@@ -3433,8 +3474,8 @@
       <c r="F5" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="14" t="n">
-        <v>13</v>
+      <c r="G5" s="16" t="s">
+        <v>68</v>
       </c>
       <c r="H5" s="14" t="n">
         <v>13</v>
@@ -3442,8 +3483,8 @@
       <c r="I5" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="J5" s="16" t="s">
-        <v>68</v>
+      <c r="J5" s="14" t="n">
+        <v>13</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>68</v>
@@ -3460,28 +3501,31 @@
       <c r="O5" s="16" t="s">
         <v>68</v>
       </c>
+      <c r="P5" s="16" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="14" t="n">
+      <c r="A6" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="E6" s="14" t="n">
         <v>32</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>33</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>33</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6" s="14" t="n">
         <v>32</v>
@@ -3499,7 +3543,7 @@
         <v>32</v>
       </c>
       <c r="M6" s="14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N6" s="14" t="n">
         <v>29</v>
@@ -3507,19 +3551,19 @@
       <c r="O6" s="14" t="n">
         <v>29</v>
       </c>
+      <c r="P6" s="14" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="12" t="n">
-        <f aca="false">SUM(C2:C6)</f>
-        <v>29</v>
-      </c>
+      <c r="C7" s="7"/>
       <c r="D7" s="12" t="n">
         <f aca="false">SUM(D2:D6)</f>
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E7" s="12" t="n">
         <f aca="false">SUM(E2:E6)</f>
@@ -3531,7 +3575,7 @@
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">SUM(G2:G6)</f>
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H7" s="12" t="n">
         <f aca="false">SUM(H2:H6)</f>
@@ -3543,7 +3587,7 @@
       </c>
       <c r="J7" s="12" t="n">
         <f aca="false">SUM(J2:J6)</f>
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K7" s="12" t="n">
         <f aca="false">SUM(K2:K6)</f>
@@ -3555,7 +3599,7 @@
       </c>
       <c r="M7" s="12" t="n">
         <f aca="false">SUM(M2:M6)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N7" s="12" t="n">
         <f aca="false">SUM(N2:N6)</f>
@@ -3565,70 +3609,85 @@
         <f aca="false">SUM(O2:O6)</f>
         <v>45</v>
       </c>
+      <c r="P7" s="12" t="n">
+        <f aca="false">SUM(P2:P6)</f>
+        <v>45</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="14" t="s">
-        <v>105</v>
-      </c>
+      <c r="C8" s="7"/>
       <c r="D8" s="14" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="O8" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1140,53 +1140,79 @@
       <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2608140900data.zip</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46248.375</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>〇の数</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>全22ファイル</t>
-        </is>
-      </c>
-      <c r="C24" s="6">
-        <f>COUNTIF(C2:C23,"〇")</f>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>全23ファイル</t>
+        </is>
+      </c>
+      <c r="C25" s="6">
+        <f>COUNTIF(C2:C24,"〇")</f>
         <v/>
       </c>
-      <c r="D24" s="6">
-        <f>COUNTIF(D2:D23,"〇")</f>
+      <c r="D25" s="6">
+        <f>COUNTIF(D2:D24,"〇")</f>
         <v/>
       </c>
-      <c r="E24" s="6">
-        <f>COUNTIF(E2:E23,"〇")</f>
+      <c r="E25" s="6">
+        <f>COUNTIF(E2:E24,"〇")</f>
         <v/>
       </c>
-      <c r="F24" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
+          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>作成: scripts/build_mlit_map_index.py</t>
         </is>
@@ -1203,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X44"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1230,6 +1256,7 @@
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="6" customWidth="1" min="23" max="23"/>
     <col width="6" customWidth="1" min="24" max="24"/>
+    <col width="6" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1353,6 +1380,11 @@
           <t>08/13 12:00</t>
         </is>
       </c>
+      <c r="Y1" s="10" t="inlineStr">
+        <is>
+          <t>08/14 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -1362,7 +1394,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>29</v>
@@ -1427,6 +1459,9 @@
       <c r="X2" s="12" t="n">
         <v>46</v>
       </c>
+      <c r="Y2" s="12" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1440,7 +1475,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>10</v>
@@ -1505,6 +1540,9 @@
       <c r="X3" s="15" t="n">
         <v>14</v>
       </c>
+      <c r="Y3" s="15" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1518,7 +1556,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>6</v>
@@ -1583,6 +1621,9 @@
       <c r="X4" s="15" t="n">
         <v>8</v>
       </c>
+      <c r="Y4" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1596,7 +1637,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>23</v>
@@ -1661,6 +1702,9 @@
       <c r="X5" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="Y5" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -1674,7 +1718,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>23</v>
@@ -1739,6 +1783,9 @@
       <c r="X6" s="15" t="n">
         <v>37</v>
       </c>
+      <c r="Y6" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -1752,7 +1799,7 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>23</v>
@@ -1817,6 +1864,9 @@
       <c r="X7" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="Y7" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -1830,7 +1880,7 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>19</v>
@@ -1895,6 +1945,9 @@
       <c r="X8" s="15" t="n">
         <v>33</v>
       </c>
+      <c r="Y8" s="15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -1908,7 +1961,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>23</v>
@@ -1973,6 +2026,9 @@
       <c r="X9" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="Y9" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -1986,7 +2042,7 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>6</v>
@@ -2051,6 +2107,9 @@
       <c r="X10" s="15" t="n">
         <v>8</v>
       </c>
+      <c r="Y10" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2064,7 +2123,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>23</v>
@@ -2129,6 +2188,9 @@
       <c r="X11" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="Y11" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2142,7 +2204,7 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>23</v>
@@ -2207,6 +2269,9 @@
       <c r="X12" s="15" t="n">
         <v>37</v>
       </c>
+      <c r="Y12" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2220,7 +2285,7 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>6</v>
@@ -2285,6 +2350,9 @@
       <c r="X13" s="15" t="n">
         <v>8</v>
       </c>
+      <c r="Y13" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2298,7 +2366,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>4</v>
@@ -2363,6 +2431,9 @@
       <c r="X14" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="Y14" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -2376,7 +2447,7 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>4</v>
@@ -2441,6 +2512,9 @@
       <c r="X15" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="Y15" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2454,7 +2528,7 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
@@ -2549,6 +2623,9 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Y16" s="15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -2562,7 +2639,7 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
@@ -2657,6 +2734,9 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Y17" s="15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -2670,7 +2750,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>23</v>
@@ -2735,6 +2815,9 @@
       <c r="X18" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="Y18" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -2748,7 +2831,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>23</v>
@@ -2813,6 +2896,9 @@
       <c r="X19" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="Y19" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -2826,7 +2912,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
@@ -2925,6 +3011,9 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Y20" s="15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -2938,7 +3027,7 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -3037,6 +3126,9 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Y21" s="15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3139,6 +3231,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -3241,6 +3338,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -3343,6 +3445,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -3445,6 +3552,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -3547,6 +3659,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -3649,6 +3766,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -3751,6 +3873,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -3853,6 +3980,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -3955,6 +4087,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -4057,6 +4194,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4175,6 +4317,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -4188,7 +4335,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
@@ -4293,6 +4440,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Y33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -4306,7 +4458,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>6</v>
@@ -4371,6 +4523,9 @@
       <c r="X34" s="15" t="n">
         <v>8</v>
       </c>
+      <c r="Y34" s="15" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -4384,7 +4539,7 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -4489,6 +4644,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Y35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -4502,7 +4662,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
@@ -4607,6 +4767,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Y36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -4725,6 +4890,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -4843,6 +5013,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -4961,6 +5136,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -5075,6 +5255,11 @@
         </is>
       </c>
       <c r="X40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="Y40" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -5112,7 +5297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5139,6 +5324,7 @@
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="6" customWidth="1" min="23" max="23"/>
     <col width="6" customWidth="1" min="24" max="24"/>
+    <col width="6" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5262,6 +5448,11 @@
           <t>08/13 12:00</t>
         </is>
       </c>
+      <c r="Y1" s="10" t="inlineStr">
+        <is>
+          <t>08/14 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -5366,6 +5557,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -5380,7 +5576,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>高速道路 62、直轄国道 42</t>
+          <t>高速道路 65、直轄国道 44</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -5446,6 +5642,9 @@
       <c r="X3" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="Y3" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -5460,7 +5659,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>高速道路 142、一般国道 7、有料道路 5</t>
+          <t>高速道路 146、一般国道 7、有料道路 6</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -5526,6 +5725,9 @@
       <c r="X4" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="Y4" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -5540,7 +5742,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>(値なし) 41</t>
+          <t>(値なし) 54</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
@@ -5640,6 +5842,9 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Y5" s="14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -5654,7 +5859,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>都道府県道 537、補助国道 57、市区町村道 41、国道445号 1</t>
+          <t>都道府県道 564、補助国道 62、市区町村道 43、国道445号 1</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -5719,6 +5924,9 @@
       </c>
       <c r="X6" s="14" t="n">
         <v>33</v>
+      </c>
+      <c r="Y6" s="14" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -5813,6 +6021,10 @@
         <f>SUM(X2:X6)</f>
         <v/>
       </c>
+      <c r="Y7" s="12">
+        <f>SUM(Y2:Y6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5923,6 +6135,11 @@
         </is>
       </c>
       <c r="X8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="Y8" s="14" t="inlineStr">
         <is>
           <t>線</t>
         </is>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1166,53 +1166,79 @@
       <c r="F24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2608170900data.zip</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>46251.375</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>〇の数</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>全23ファイル</t>
-        </is>
-      </c>
-      <c r="C25" s="6">
-        <f>COUNTIF(C2:C24,"〇")</f>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>全24ファイル</t>
+        </is>
+      </c>
+      <c r="C26" s="6">
+        <f>COUNTIF(C2:C25,"〇")</f>
         <v/>
       </c>
-      <c r="D25" s="6">
-        <f>COUNTIF(D2:D24,"〇")</f>
+      <c r="D26" s="6">
+        <f>COUNTIF(D2:D25,"〇")</f>
         <v/>
       </c>
-      <c r="E25" s="6">
-        <f>COUNTIF(E2:E24,"〇")</f>
+      <c r="E26" s="6">
+        <f>COUNTIF(E2:E25,"〇")</f>
         <v/>
       </c>
-      <c r="F25" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
+          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>作成: scripts/build_mlit_map_index.py</t>
         </is>
@@ -1229,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Z44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1257,6 +1283,7 @@
     <col width="6" customWidth="1" min="23" max="23"/>
     <col width="6" customWidth="1" min="24" max="24"/>
     <col width="6" customWidth="1" min="25" max="25"/>
+    <col width="6" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1385,6 +1412,11 @@
           <t>08/14 09:00</t>
         </is>
       </c>
+      <c r="Z1" s="10" t="inlineStr">
+        <is>
+          <t>08/17 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -1394,7 +1426,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>29</v>
@@ -1462,6 +1494,9 @@
       <c r="Y2" s="12" t="n">
         <v>57</v>
       </c>
+      <c r="Z2" s="12" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1475,7 +1510,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>10</v>
@@ -1543,6 +1578,9 @@
       <c r="Y3" s="15" t="n">
         <v>24</v>
       </c>
+      <c r="Z3" s="15" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1556,7 +1594,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>6</v>
@@ -1624,6 +1662,9 @@
       <c r="Y4" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="Z4" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1637,7 +1678,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>23</v>
@@ -1705,6 +1746,9 @@
       <c r="Y5" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="Z5" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -1718,7 +1762,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>23</v>
@@ -1786,6 +1830,9 @@
       <c r="Y6" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="Z6" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -1799,7 +1846,7 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>23</v>
@@ -1867,6 +1914,9 @@
       <c r="Y7" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="Z7" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -1880,7 +1930,7 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>19</v>
@@ -1948,6 +1998,9 @@
       <c r="Y8" s="15" t="n">
         <v>34</v>
       </c>
+      <c r="Z8" s="15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -1961,7 +2014,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>23</v>
@@ -2029,6 +2082,9 @@
       <c r="Y9" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="Z9" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2042,7 +2098,7 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>6</v>
@@ -2110,6 +2166,9 @@
       <c r="Y10" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="Z10" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2123,7 +2182,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>23</v>
@@ -2191,6 +2250,9 @@
       <c r="Y11" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="Z11" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2204,7 +2266,7 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>23</v>
@@ -2272,6 +2334,9 @@
       <c r="Y12" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="Z12" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2285,7 +2350,7 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>6</v>
@@ -2353,6 +2418,9 @@
       <c r="Y13" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="Z13" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2366,7 +2434,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>4</v>
@@ -2434,6 +2502,9 @@
       <c r="Y14" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="Z14" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -2447,7 +2518,7 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>4</v>
@@ -2515,6 +2586,9 @@
       <c r="Y15" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="Z15" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2528,7 +2602,7 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
@@ -2626,6 +2700,11 @@
       <c r="Y16" s="15" t="n">
         <v>44</v>
       </c>
+      <c r="Z16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -2639,7 +2718,7 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
@@ -2737,6 +2816,11 @@
       <c r="Y17" s="15" t="n">
         <v>44</v>
       </c>
+      <c r="Z17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -2750,7 +2834,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>23</v>
@@ -2818,6 +2902,9 @@
       <c r="Y18" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="Z18" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -2831,7 +2918,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>23</v>
@@ -2899,6 +2986,9 @@
       <c r="Y19" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="Z19" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -2912,7 +3002,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
@@ -3014,6 +3104,11 @@
       <c r="Y20" s="15" t="n">
         <v>44</v>
       </c>
+      <c r="Z20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3027,7 +3122,7 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -3129,6 +3224,11 @@
       <c r="Y21" s="15" t="n">
         <v>44</v>
       </c>
+      <c r="Z21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3236,6 +3336,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -3343,6 +3448,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -3450,6 +3560,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -3557,6 +3672,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -3664,6 +3784,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -3771,6 +3896,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -3878,6 +4008,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -3985,6 +4120,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -4092,6 +4232,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -4199,6 +4344,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4322,6 +4472,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -4335,7 +4490,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
@@ -4445,6 +4600,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Z33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -4458,7 +4618,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>6</v>
@@ -4526,6 +4686,9 @@
       <c r="Y34" s="15" t="n">
         <v>18</v>
       </c>
+      <c r="Z34" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -4539,7 +4702,7 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -4649,6 +4812,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Z35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -4662,7 +4830,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
@@ -4772,6 +4940,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="Z36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -4895,6 +5068,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -5018,6 +5196,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -5141,6 +5324,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -5260,6 +5448,11 @@
         </is>
       </c>
       <c r="Y40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="Z40" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -5297,7 +5490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5325,6 +5518,7 @@
     <col width="6" customWidth="1" min="23" max="23"/>
     <col width="6" customWidth="1" min="24" max="24"/>
     <col width="6" customWidth="1" min="25" max="25"/>
+    <col width="6" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5453,6 +5647,11 @@
           <t>08/14 09:00</t>
         </is>
       </c>
+      <c r="Z1" s="10" t="inlineStr">
+        <is>
+          <t>08/17 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -5562,6 +5761,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="Z2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -5576,7 +5780,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>高速道路 65、直轄国道 44</t>
+          <t>高速道路 68、直轄国道 46</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -5645,6 +5849,9 @@
       <c r="Y3" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="Z3" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -5659,7 +5866,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>高速道路 146、一般国道 7、有料道路 6</t>
+          <t>高速道路 150、一般国道 7、有料道路 7</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -5728,6 +5935,9 @@
       <c r="Y4" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="Z4" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -5845,6 +6055,11 @@
       <c r="Y5" s="14" t="n">
         <v>13</v>
       </c>
+      <c r="Z5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -5859,7 +6074,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>都道府県道 564、補助国道 62、市区町村道 43、国道445号 1</t>
+          <t>都道府県道 591、補助国道 67、市区町村道 45、国道445号 1</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -5926,6 +6141,9 @@
         <v>33</v>
       </c>
       <c r="Y6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z6" s="14" t="n">
         <v>34</v>
       </c>
     </row>
@@ -6025,6 +6243,10 @@
         <f>SUM(Y2:Y6)</f>
         <v/>
       </c>
+      <c r="Z7" s="12">
+        <f>SUM(Z2:Z6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6140,6 +6362,11 @@
         </is>
       </c>
       <c r="Y8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="Z8" s="14" t="inlineStr">
         <is>
           <t>線</t>
         </is>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1192,53 +1192,79 @@
       <c r="F25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2608180900data.zip</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>46252.375</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>〇の数</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>全24ファイル</t>
-        </is>
-      </c>
-      <c r="C26" s="6">
-        <f>COUNTIF(C2:C25,"〇")</f>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>全25ファイル</t>
+        </is>
+      </c>
+      <c r="C27" s="6">
+        <f>COUNTIF(C2:C26,"〇")</f>
         <v/>
       </c>
-      <c r="D26" s="6">
-        <f>COUNTIF(D2:D25,"〇")</f>
+      <c r="D27" s="6">
+        <f>COUNTIF(D2:D26,"〇")</f>
         <v/>
       </c>
-      <c r="E26" s="6">
-        <f>COUNTIF(E2:E25,"〇")</f>
+      <c r="E27" s="6">
+        <f>COUNTIF(E2:E26,"〇")</f>
         <v/>
       </c>
-      <c r="F26" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
-        </is>
-      </c>
+      <c r="F27" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
+          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>作成: scripts/build_mlit_map_index.py</t>
         </is>
@@ -1255,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1284,6 +1310,7 @@
     <col width="6" customWidth="1" min="24" max="24"/>
     <col width="6" customWidth="1" min="25" max="25"/>
     <col width="6" customWidth="1" min="26" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1417,6 +1444,11 @@
           <t>08/17 09:00</t>
         </is>
       </c>
+      <c r="AA1" s="10" t="inlineStr">
+        <is>
+          <t>08/18 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -1426,7 +1458,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>29</v>
@@ -1497,6 +1529,9 @@
       <c r="Z2" s="12" t="n">
         <v>44</v>
       </c>
+      <c r="AA2" s="12" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1510,7 +1545,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>10</v>
@@ -1581,6 +1616,9 @@
       <c r="Z3" s="15" t="n">
         <v>11</v>
       </c>
+      <c r="AA3" s="15" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1594,7 +1632,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>6</v>
@@ -1665,6 +1703,9 @@
       <c r="Z4" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AA4" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1678,7 +1719,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>23</v>
@@ -1749,6 +1790,9 @@
       <c r="Z5" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AA5" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -1762,7 +1806,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>23</v>
@@ -1833,6 +1877,9 @@
       <c r="Z6" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AA6" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -1846,7 +1893,7 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>23</v>
@@ -1917,6 +1964,9 @@
       <c r="Z7" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AA7" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -1930,7 +1980,7 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>19</v>
@@ -2001,6 +2051,9 @@
       <c r="Z8" s="15" t="n">
         <v>34</v>
       </c>
+      <c r="AA8" s="15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2014,7 +2067,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>23</v>
@@ -2085,6 +2138,9 @@
       <c r="Z9" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AA9" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2098,7 +2154,7 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>6</v>
@@ -2169,6 +2225,9 @@
       <c r="Z10" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AA10" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2182,7 +2241,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>23</v>
@@ -2253,6 +2312,9 @@
       <c r="Z11" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AA11" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2266,7 +2328,7 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>23</v>
@@ -2337,6 +2399,9 @@
       <c r="Z12" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AA12" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2350,7 +2415,7 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>6</v>
@@ -2421,6 +2486,9 @@
       <c r="Z13" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AA13" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2434,7 +2502,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>4</v>
@@ -2505,6 +2573,9 @@
       <c r="Z14" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AA14" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -2518,7 +2589,7 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>4</v>
@@ -2589,6 +2660,9 @@
       <c r="Z15" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AA15" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2602,7 +2676,7 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
@@ -2705,6 +2779,9 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AA16" s="15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -2718,7 +2795,7 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
@@ -2821,6 +2898,9 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AA17" s="15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -2834,7 +2914,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>23</v>
@@ -2905,6 +2985,9 @@
       <c r="Z18" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AA18" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -2918,7 +3001,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>23</v>
@@ -2989,6 +3072,9 @@
       <c r="Z19" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AA19" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3002,7 +3088,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
@@ -3109,6 +3195,9 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AA20" s="15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3122,7 +3211,7 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -3229,6 +3318,9 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AA21" s="15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3341,6 +3433,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -3453,6 +3550,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -3565,6 +3667,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -3677,6 +3784,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -3789,6 +3901,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -3901,6 +4018,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -4013,6 +4135,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -4125,6 +4252,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -4237,6 +4369,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -4349,6 +4486,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4477,6 +4619,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -4490,7 +4637,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
@@ -4605,6 +4752,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AA33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -4618,7 +4770,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>6</v>
@@ -4689,6 +4841,9 @@
       <c r="Z34" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AA34" s="15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -4702,7 +4857,7 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -4817,6 +4972,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AA35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -4830,7 +4990,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
@@ -4945,6 +5105,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AA36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -5073,6 +5238,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -5201,6 +5371,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -5329,6 +5504,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -5453,6 +5633,11 @@
         </is>
       </c>
       <c r="Z40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AA40" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -5490,7 +5675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5519,6 +5704,7 @@
     <col width="6" customWidth="1" min="24" max="24"/>
     <col width="6" customWidth="1" min="25" max="25"/>
     <col width="6" customWidth="1" min="26" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5652,6 +5838,11 @@
           <t>08/17 09:00</t>
         </is>
       </c>
+      <c r="AA1" s="10" t="inlineStr">
+        <is>
+          <t>08/18 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -5766,6 +5957,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -5780,7 +5976,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>高速道路 68、直轄国道 46</t>
+          <t>高速道路 71、直轄国道 48</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -5852,6 +6048,9 @@
       <c r="Z3" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AA3" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -5866,7 +6065,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>高速道路 150、一般国道 7、有料道路 7</t>
+          <t>高速道路 154、有料道路 8、一般国道 7</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -5938,6 +6137,9 @@
       <c r="Z4" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AA4" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -5952,7 +6154,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>(値なし) 54</t>
+          <t>(値なし) 56</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
@@ -6060,6 +6262,9 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AA5" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -6074,7 +6279,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>都道府県道 591、補助国道 67、市区町村道 45、国道445号 1</t>
+          <t>都道府県道 618、補助国道 72、市区町村道 47、国道445号 1</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -6144,6 +6349,9 @@
         <v>34</v>
       </c>
       <c r="Z6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA6" s="14" t="n">
         <v>34</v>
       </c>
     </row>
@@ -6247,6 +6455,10 @@
         <f>SUM(Z2:Z6)</f>
         <v/>
       </c>
+      <c r="AA7" s="12">
+        <f>SUM(AA2:AA6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6367,6 +6579,11 @@
         </is>
       </c>
       <c r="Z8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AA8" s="14" t="inlineStr">
         <is>
           <t>線</t>
         </is>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1218,53 +1218,105 @@
       <c r="F26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2608190900data.zip</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>46253.375</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2608200900data.zip</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46254.375</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>〇の数</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>全25ファイル</t>
-        </is>
-      </c>
-      <c r="C27" s="6">
-        <f>COUNTIF(C2:C26,"〇")</f>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>全27ファイル</t>
+        </is>
+      </c>
+      <c r="C29" s="6">
+        <f>COUNTIF(C2:C28,"〇")</f>
         <v/>
       </c>
-      <c r="D27" s="6">
-        <f>COUNTIF(D2:D26,"〇")</f>
+      <c r="D29" s="6">
+        <f>COUNTIF(D2:D28,"〇")</f>
         <v/>
       </c>
-      <c r="E27" s="6">
-        <f>COUNTIF(E2:E26,"〇")</f>
+      <c r="E29" s="6">
+        <f>COUNTIF(E2:E28,"〇")</f>
         <v/>
       </c>
-      <c r="F27" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
-        </is>
-      </c>
+      <c r="F29" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>作成: scripts/build_mlit_map_index.py</t>
         </is>
@@ -1281,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1311,6 +1363,8 @@
     <col width="6" customWidth="1" min="25" max="25"/>
     <col width="6" customWidth="1" min="26" max="26"/>
     <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="6" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1449,6 +1503,16 @@
           <t>08/18 09:00</t>
         </is>
       </c>
+      <c r="AB1" s="10" t="inlineStr">
+        <is>
+          <t>08/19 09:00</t>
+        </is>
+      </c>
+      <c r="AC1" s="10" t="inlineStr">
+        <is>
+          <t>08/20 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -1458,7 +1522,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>29</v>
@@ -1532,6 +1596,12 @@
       <c r="AA2" s="12" t="n">
         <v>46</v>
       </c>
+      <c r="AB2" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC2" s="12" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1545,7 +1615,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>10</v>
@@ -1619,6 +1689,12 @@
       <c r="AA3" s="15" t="n">
         <v>13</v>
       </c>
+      <c r="AB3" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1632,7 +1708,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>6</v>
@@ -1706,6 +1782,12 @@
       <c r="AA4" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AB4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC4" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1719,7 +1801,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>23</v>
@@ -1793,6 +1875,12 @@
       <c r="AA5" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AB5" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC5" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -1806,7 +1894,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>23</v>
@@ -1880,6 +1968,12 @@
       <c r="AA6" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AB6" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC6" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -1893,7 +1987,7 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>23</v>
@@ -1967,6 +2061,12 @@
       <c r="AA7" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AB7" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC7" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -1980,7 +2080,7 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>19</v>
@@ -2054,6 +2154,12 @@
       <c r="AA8" s="15" t="n">
         <v>34</v>
       </c>
+      <c r="AB8" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC8" s="15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2067,7 +2173,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>23</v>
@@ -2141,6 +2247,12 @@
       <c r="AA9" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AB9" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2154,7 +2266,7 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>6</v>
@@ -2228,6 +2340,12 @@
       <c r="AA10" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AB10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2241,7 +2359,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>23</v>
@@ -2315,6 +2433,12 @@
       <c r="AA11" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AB11" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC11" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2328,7 +2452,7 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>23</v>
@@ -2402,6 +2526,12 @@
       <c r="AA12" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AB12" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC12" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2415,7 +2545,7 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>6</v>
@@ -2489,6 +2619,12 @@
       <c r="AA13" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AB13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC13" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2502,7 +2638,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>4</v>
@@ -2576,6 +2712,12 @@
       <c r="AA14" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AB14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -2589,7 +2731,7 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>4</v>
@@ -2663,6 +2805,12 @@
       <c r="AA15" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AB15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC15" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2676,7 +2824,7 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
@@ -2782,6 +2930,16 @@
       <c r="AA16" s="15" t="n">
         <v>44</v>
       </c>
+      <c r="AB16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AC16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -2795,7 +2953,7 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
@@ -2901,6 +3059,16 @@
       <c r="AA17" s="15" t="n">
         <v>44</v>
       </c>
+      <c r="AB17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AC17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -2914,7 +3082,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>23</v>
@@ -2988,6 +3156,12 @@
       <c r="AA18" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AB18" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC18" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -3001,7 +3175,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>23</v>
@@ -3075,6 +3249,12 @@
       <c r="AA19" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AB19" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC19" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3088,7 +3268,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
@@ -3198,6 +3378,16 @@
       <c r="AA20" s="15" t="n">
         <v>44</v>
       </c>
+      <c r="AB20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AC20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3211,7 +3401,7 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -3321,6 +3511,16 @@
       <c r="AA21" s="15" t="n">
         <v>44</v>
       </c>
+      <c r="AB21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AC21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3438,6 +3638,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -3555,6 +3765,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -3672,6 +3892,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -3789,6 +4019,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -3906,6 +4146,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -4023,6 +4273,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -4140,6 +4400,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -4257,6 +4527,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -4374,6 +4654,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -4491,6 +4781,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4624,6 +4924,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -4637,7 +4947,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
@@ -4757,6 +5067,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AB33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AC33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -4770,7 +5090,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>6</v>
@@ -4844,6 +5164,12 @@
       <c r="AA34" s="15" t="n">
         <v>7</v>
       </c>
+      <c r="AB34" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC34" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -4857,7 +5183,7 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -4977,6 +5303,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AB35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AC35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -4990,7 +5326,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
@@ -5110,6 +5446,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AB36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AC36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -5243,6 +5589,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -5376,6 +5732,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -5509,6 +5875,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -5638,6 +6014,16 @@
         </is>
       </c>
       <c r="AA40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AB40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC40" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -5675,7 +6061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5705,6 +6091,8 @@
     <col width="6" customWidth="1" min="25" max="25"/>
     <col width="6" customWidth="1" min="26" max="26"/>
     <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="6" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5843,6 +6231,16 @@
           <t>08/18 09:00</t>
         </is>
       </c>
+      <c r="AB1" s="10" t="inlineStr">
+        <is>
+          <t>08/19 09:00</t>
+        </is>
+      </c>
+      <c r="AC1" s="10" t="inlineStr">
+        <is>
+          <t>08/20 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -5962,6 +6360,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AB2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -5976,7 +6384,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>高速道路 71、直轄国道 48</t>
+          <t>高速道路 77、直轄国道 52</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -6051,6 +6459,12 @@
       <c r="AA3" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AB3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC3" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -6065,7 +6479,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>高速道路 154、有料道路 8、一般国道 7</t>
+          <t>高速道路 162、有料道路 10、一般国道 7</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -6140,6 +6554,12 @@
       <c r="AA4" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AB4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC4" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -6265,6 +6685,16 @@
       <c r="AA5" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="AB5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AC5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -6279,7 +6709,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>都道府県道 618、補助国道 72、市区町村道 47、国道445号 1</t>
+          <t>都道府県道 672、補助国道 82、市区町村道 51、国道445号 1</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -6352,6 +6782,12 @@
         <v>34</v>
       </c>
       <c r="AA6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC6" s="14" t="n">
         <v>34</v>
       </c>
     </row>
@@ -6459,6 +6895,14 @@
         <f>SUM(AA2:AA6)</f>
         <v/>
       </c>
+      <c r="AB7" s="12">
+        <f>SUM(AB2:AB6)</f>
+        <v/>
+      </c>
+      <c r="AC7" s="12">
+        <f>SUM(AC2:AC6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6584,6 +7028,16 @@
         </is>
       </c>
       <c r="AA8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AB8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AC8" s="14" t="inlineStr">
         <is>
           <t>線</t>
         </is>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1270,53 +1270,79 @@
       <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2608210900data.zip</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46255.375</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>〇の数</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>全27ファイル</t>
-        </is>
-      </c>
-      <c r="C29" s="6">
-        <f>COUNTIF(C2:C28,"〇")</f>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>全28ファイル</t>
+        </is>
+      </c>
+      <c r="C30" s="6">
+        <f>COUNTIF(C2:C29,"〇")</f>
         <v/>
       </c>
-      <c r="D29" s="6">
-        <f>COUNTIF(D2:D28,"〇")</f>
+      <c r="D30" s="6">
+        <f>COUNTIF(D2:D29,"〇")</f>
         <v/>
       </c>
-      <c r="E29" s="6">
-        <f>COUNTIF(E2:E28,"〇")</f>
+      <c r="E30" s="6">
+        <f>COUNTIF(E2:E29,"〇")</f>
         <v/>
       </c>
-      <c r="F29" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
-        </is>
-      </c>
+      <c r="F30" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
+          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>作成: scripts/build_mlit_map_index.py</t>
         </is>
@@ -1333,7 +1359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AD44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1365,6 +1391,7 @@
     <col width="6" customWidth="1" min="27" max="27"/>
     <col width="6" customWidth="1" min="28" max="28"/>
     <col width="6" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1513,6 +1540,11 @@
           <t>08/20 09:00</t>
         </is>
       </c>
+      <c r="AD1" s="10" t="inlineStr">
+        <is>
+          <t>08/21 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -1522,7 +1554,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>29</v>
@@ -1602,6 +1634,9 @@
       <c r="AC2" s="12" t="n">
         <v>44</v>
       </c>
+      <c r="AD2" s="12" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1615,7 +1650,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>10</v>
@@ -1695,6 +1730,9 @@
       <c r="AC3" s="15" t="n">
         <v>11</v>
       </c>
+      <c r="AD3" s="15" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1708,7 +1746,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>6</v>
@@ -1788,6 +1826,9 @@
       <c r="AC4" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AD4" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1801,7 +1842,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>23</v>
@@ -1881,6 +1922,9 @@
       <c r="AC5" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AD5" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -1894,7 +1938,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>23</v>
@@ -1974,6 +2018,9 @@
       <c r="AC6" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AD6" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -1987,7 +2034,7 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>23</v>
@@ -2067,6 +2114,9 @@
       <c r="AC7" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AD7" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -2080,7 +2130,7 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>19</v>
@@ -2160,6 +2210,9 @@
       <c r="AC8" s="15" t="n">
         <v>34</v>
       </c>
+      <c r="AD8" s="15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2173,7 +2226,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>23</v>
@@ -2253,6 +2306,9 @@
       <c r="AC9" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AD9" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2266,7 +2322,7 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>6</v>
@@ -2346,6 +2402,9 @@
       <c r="AC10" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AD10" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2359,7 +2418,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>23</v>
@@ -2439,6 +2498,9 @@
       <c r="AC11" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AD11" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2452,7 +2514,7 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>23</v>
@@ -2532,6 +2594,9 @@
       <c r="AC12" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AD12" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2545,7 +2610,7 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>6</v>
@@ -2625,6 +2690,9 @@
       <c r="AC13" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AD13" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2638,7 +2706,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>4</v>
@@ -2718,6 +2786,9 @@
       <c r="AC14" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AD14" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -2731,7 +2802,7 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>4</v>
@@ -2811,6 +2882,9 @@
       <c r="AC15" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AD15" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2824,7 +2898,7 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
@@ -2940,6 +3014,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AD16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -2953,7 +3032,7 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
@@ -3069,6 +3148,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AD17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -3082,7 +3166,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>23</v>
@@ -3162,6 +3246,9 @@
       <c r="AC18" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AD18" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -3175,7 +3262,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>23</v>
@@ -3255,6 +3342,9 @@
       <c r="AC19" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AD19" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3268,7 +3358,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
@@ -3388,6 +3478,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AD20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3401,7 +3496,7 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -3521,6 +3616,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AD21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3648,6 +3748,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -3775,6 +3880,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -3902,6 +4012,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -4029,6 +4144,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -4156,6 +4276,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -4283,6 +4408,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -4410,6 +4540,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -4537,6 +4672,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -4664,6 +4804,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -4791,6 +4936,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4934,6 +5084,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -4947,7 +5102,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
@@ -5077,6 +5232,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AD33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -5090,7 +5250,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>6</v>
@@ -5170,6 +5330,9 @@
       <c r="AC34" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AD34" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -5183,7 +5346,7 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -5313,6 +5476,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AD35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -5326,7 +5494,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
@@ -5456,6 +5624,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AD36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -5599,6 +5772,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -5742,6 +5920,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -5885,6 +6068,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -6024,6 +6212,11 @@
         </is>
       </c>
       <c r="AC40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AD40" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -6061,7 +6254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6093,6 +6286,7 @@
     <col width="6" customWidth="1" min="27" max="27"/>
     <col width="6" customWidth="1" min="28" max="28"/>
     <col width="6" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6241,6 +6435,11 @@
           <t>08/20 09:00</t>
         </is>
       </c>
+      <c r="AD1" s="10" t="inlineStr">
+        <is>
+          <t>08/21 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -6370,6 +6569,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -6384,7 +6588,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>高速道路 77、直轄国道 52</t>
+          <t>高速道路 80、直轄国道 54</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -6465,6 +6669,9 @@
       <c r="AC3" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AD3" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -6479,7 +6686,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>高速道路 162、有料道路 10、一般国道 7</t>
+          <t>高速道路 166、有料道路 11、一般国道 7</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -6560,6 +6767,9 @@
       <c r="AC4" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AD4" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -6695,6 +6905,11 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AD5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -6709,7 +6924,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>都道府県道 672、補助国道 82、市区町村道 51、国道445号 1</t>
+          <t>都道府県道 699、補助国道 87、市区町村道 53、国道445号 1</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -6788,6 +7003,9 @@
         <v>34</v>
       </c>
       <c r="AC6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD6" s="14" t="n">
         <v>34</v>
       </c>
     </row>
@@ -6903,6 +7121,10 @@
         <f>SUM(AC2:AC6)</f>
         <v/>
       </c>
+      <c r="AD7" s="12">
+        <f>SUM(AD2:AD6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -7038,6 +7260,11 @@
         </is>
       </c>
       <c r="AC8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AD8" s="14" t="inlineStr">
         <is>
           <t>線</t>
         </is>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1296,53 +1296,105 @@
       <c r="F29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2608230900data.zip</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46257.375</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2608250900data.zip</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>46259.375</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>〇の数</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>全28ファイル</t>
-        </is>
-      </c>
-      <c r="C30" s="6">
-        <f>COUNTIF(C2:C29,"〇")</f>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>全30ファイル</t>
+        </is>
+      </c>
+      <c r="C32" s="6">
+        <f>COUNTIF(C2:C31,"〇")</f>
         <v/>
       </c>
-      <c r="D30" s="6">
-        <f>COUNTIF(D2:D29,"〇")</f>
+      <c r="D32" s="6">
+        <f>COUNTIF(D2:D31,"〇")</f>
         <v/>
       </c>
-      <c r="E30" s="6">
-        <f>COUNTIF(E2:E29,"〇")</f>
+      <c r="E32" s="6">
+        <f>COUNTIF(E2:E31,"〇")</f>
         <v/>
       </c>
-      <c r="F30" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
-        </is>
-      </c>
+      <c r="F32" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>作成: scripts/build_mlit_map_index.py</t>
         </is>
@@ -1359,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD44"/>
+  <dimension ref="A1:AF44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1392,6 +1444,8 @@
     <col width="6" customWidth="1" min="28" max="28"/>
     <col width="6" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1545,6 +1599,16 @@
           <t>08/21 09:00</t>
         </is>
       </c>
+      <c r="AE1" s="10" t="inlineStr">
+        <is>
+          <t>08/23 09:00</t>
+        </is>
+      </c>
+      <c r="AF1" s="10" t="inlineStr">
+        <is>
+          <t>08/25 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -1554,7 +1618,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>29</v>
@@ -1637,6 +1701,12 @@
       <c r="AD2" s="12" t="n">
         <v>44</v>
       </c>
+      <c r="AE2" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF2" s="12" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1650,7 +1720,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>10</v>
@@ -1733,6 +1803,12 @@
       <c r="AD3" s="15" t="n">
         <v>11</v>
       </c>
+      <c r="AE3" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1746,7 +1822,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>6</v>
@@ -1829,6 +1905,12 @@
       <c r="AD4" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AE4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1842,7 +1924,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>23</v>
@@ -1925,6 +2007,12 @@
       <c r="AD5" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AE5" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF5" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -1938,7 +2026,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>23</v>
@@ -2021,6 +2109,12 @@
       <c r="AD6" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AE6" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF6" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -2034,7 +2128,7 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>23</v>
@@ -2117,6 +2211,12 @@
       <c r="AD7" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AE7" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF7" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -2130,7 +2230,7 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>19</v>
@@ -2213,6 +2313,12 @@
       <c r="AD8" s="15" t="n">
         <v>34</v>
       </c>
+      <c r="AE8" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF8" s="15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2226,7 +2332,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>23</v>
@@ -2309,6 +2415,12 @@
       <c r="AD9" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AE9" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF9" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2322,7 +2434,7 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>6</v>
@@ -2405,6 +2517,12 @@
       <c r="AD10" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AE10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2418,7 +2536,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>23</v>
@@ -2501,6 +2619,12 @@
       <c r="AD11" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AE11" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF11" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2514,7 +2638,7 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>23</v>
@@ -2597,6 +2721,12 @@
       <c r="AD12" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AE12" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF12" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2610,7 +2740,7 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>6</v>
@@ -2693,6 +2823,12 @@
       <c r="AD13" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AE13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF13" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2706,7 +2842,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>4</v>
@@ -2789,6 +2925,12 @@
       <c r="AD14" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AE14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -2802,7 +2944,7 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>4</v>
@@ -2885,6 +3027,12 @@
       <c r="AD15" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AE15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2898,7 +3046,7 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
@@ -3019,6 +3167,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AE16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AF16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -3032,7 +3190,7 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
@@ -3153,6 +3311,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AE17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AF17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -3166,7 +3334,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>23</v>
@@ -3249,6 +3417,12 @@
       <c r="AD18" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AE18" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF18" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -3262,7 +3436,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>23</v>
@@ -3345,6 +3519,12 @@
       <c r="AD19" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AE19" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF19" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3358,7 +3538,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
@@ -3483,6 +3663,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AE20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AF20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3496,7 +3686,7 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -3621,6 +3811,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AE21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AF21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3753,6 +3953,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -3885,6 +4095,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -4017,6 +4237,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -4149,6 +4379,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -4281,6 +4521,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -4413,6 +4663,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -4545,6 +4805,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -4677,6 +4947,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -4809,6 +5089,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -4941,6 +5231,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -5089,6 +5389,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -5102,7 +5412,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
@@ -5237,6 +5547,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AE33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AF33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -5250,7 +5570,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>6</v>
@@ -5333,6 +5653,12 @@
       <c r="AD34" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AE34" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF34" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -5346,7 +5672,7 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -5481,6 +5807,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AE35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AF35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -5494,7 +5830,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
@@ -5629,6 +5965,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AE36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AF36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -5777,6 +6123,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -5925,6 +6281,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -6073,6 +6439,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -6217,6 +6593,16 @@
         </is>
       </c>
       <c r="AD40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AE40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF40" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -6254,7 +6640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6287,6 +6673,8 @@
     <col width="6" customWidth="1" min="28" max="28"/>
     <col width="6" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6440,6 +6828,16 @@
           <t>08/21 09:00</t>
         </is>
       </c>
+      <c r="AE1" s="10" t="inlineStr">
+        <is>
+          <t>08/23 09:00</t>
+        </is>
+      </c>
+      <c r="AF1" s="10" t="inlineStr">
+        <is>
+          <t>08/25 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -6574,6 +6972,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -6588,7 +6996,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>高速道路 80、直轄国道 54</t>
+          <t>高速道路 86、直轄国道 58</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -6672,6 +7080,12 @@
       <c r="AD3" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AE3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -6686,7 +7100,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>高速道路 166、有料道路 11、一般国道 7</t>
+          <t>高速道路 174、有料道路 13、一般国道 7</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -6770,6 +7184,12 @@
       <c r="AD4" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AE4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -6910,6 +7330,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AE5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AF5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -6924,7 +7354,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>都道府県道 699、補助国道 87、市区町村道 53、国道445号 1</t>
+          <t>都道府県道 753、補助国道 97、市区町村道 57、国道445号 1</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -7006,6 +7436,12 @@
         <v>34</v>
       </c>
       <c r="AD6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF6" s="14" t="n">
         <v>34</v>
       </c>
     </row>
@@ -7125,6 +7561,14 @@
         <f>SUM(AD2:AD6)</f>
         <v/>
       </c>
+      <c r="AE7" s="12">
+        <f>SUM(AE2:AE6)</f>
+        <v/>
+      </c>
+      <c r="AF7" s="12">
+        <f>SUM(AF2:AF6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -7265,6 +7709,16 @@
         </is>
       </c>
       <c r="AD8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AE8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AF8" s="14" t="inlineStr">
         <is>
           <t>線</t>
         </is>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1348,53 +1348,97 @@
       <c r="F31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2608270900data.zip</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>46261.375</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2608311600data.zip</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46265.66666666666</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>〇の数</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>全30ファイル</t>
-        </is>
-      </c>
-      <c r="C32" s="6">
-        <f>COUNTIF(C2:C31,"〇")</f>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>全32ファイル</t>
+        </is>
+      </c>
+      <c r="C34" s="6">
+        <f>COUNTIF(C2:C33,"〇")</f>
         <v/>
       </c>
-      <c r="D32" s="6">
-        <f>COUNTIF(D2:D31,"〇")</f>
+      <c r="D34" s="6">
+        <f>COUNTIF(D2:D33,"〇")</f>
         <v/>
       </c>
-      <c r="E32" s="6">
-        <f>COUNTIF(E2:E31,"〇")</f>
+      <c r="E34" s="6">
+        <f>COUNTIF(E2:E33,"〇")</f>
         <v/>
       </c>
-      <c r="F32" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
-        </is>
-      </c>
+      <c r="F34" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>作成: scripts/build_mlit_map_index.py</t>
         </is>
@@ -1411,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF44"/>
+  <dimension ref="A1:AH44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1446,6 +1490,8 @@
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
     <col width="6" customWidth="1" min="32" max="32"/>
+    <col width="6" customWidth="1" min="33" max="33"/>
+    <col width="6" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1609,6 +1655,16 @@
           <t>08/25 09:00</t>
         </is>
       </c>
+      <c r="AG1" s="10" t="inlineStr">
+        <is>
+          <t>08/27 09:00</t>
+        </is>
+      </c>
+      <c r="AH1" s="10" t="inlineStr">
+        <is>
+          <t>08/31 16:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -1618,7 +1674,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>29</v>
@@ -1707,6 +1763,12 @@
       <c r="AF2" s="12" t="n">
         <v>44</v>
       </c>
+      <c r="AG2" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH2" s="12" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1720,7 +1782,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>10</v>
@@ -1809,6 +1871,12 @@
       <c r="AF3" s="15" t="n">
         <v>11</v>
       </c>
+      <c r="AG3" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1822,7 +1890,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>6</v>
@@ -1911,6 +1979,12 @@
       <c r="AF4" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AG4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1924,7 +1998,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>23</v>
@@ -2013,6 +2087,12 @@
       <c r="AF5" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AG5" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AH5" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -2026,7 +2106,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>23</v>
@@ -2115,6 +2195,12 @@
       <c r="AF6" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AG6" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH6" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -2128,7 +2214,7 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>23</v>
@@ -2217,6 +2303,12 @@
       <c r="AF7" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AG7" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AH7" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -2230,7 +2322,7 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>19</v>
@@ -2319,6 +2411,12 @@
       <c r="AF8" s="15" t="n">
         <v>34</v>
       </c>
+      <c r="AG8" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH8" s="15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2332,7 +2430,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>23</v>
@@ -2421,6 +2519,12 @@
       <c r="AF9" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AG9" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AH9" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2434,7 +2538,7 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>6</v>
@@ -2523,6 +2627,12 @@
       <c r="AF10" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AG10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2536,7 +2646,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>23</v>
@@ -2625,6 +2735,12 @@
       <c r="AF11" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AG11" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AH11" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2638,7 +2754,7 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>23</v>
@@ -2727,6 +2843,12 @@
       <c r="AF12" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AG12" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH12" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2740,7 +2862,7 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>6</v>
@@ -2829,6 +2951,12 @@
       <c r="AF13" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AG13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH13" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2842,7 +2970,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>4</v>
@@ -2931,6 +3059,12 @@
       <c r="AF14" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AG14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -2944,7 +3078,7 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>4</v>
@@ -3033,6 +3167,12 @@
       <c r="AF15" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AG15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH15" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -3046,7 +3186,7 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
@@ -3177,6 +3317,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AG16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AH16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -3190,7 +3340,7 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
@@ -3321,6 +3471,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AG17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AH17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -3334,7 +3494,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>23</v>
@@ -3423,6 +3583,12 @@
       <c r="AF18" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AG18" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AH18" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -3436,7 +3602,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>23</v>
@@ -3525,6 +3691,12 @@
       <c r="AF19" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AG19" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AH19" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3538,7 +3710,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
@@ -3673,6 +3845,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AG20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AH20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3686,7 +3868,7 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -3821,6 +4003,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AG21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AH21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3963,6 +4155,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -4105,6 +4307,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -4247,6 +4459,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -4389,6 +4611,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -4531,6 +4763,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -4673,6 +4915,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -4815,6 +5067,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -4957,6 +5219,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -5099,6 +5371,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -5241,6 +5523,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -5399,6 +5691,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -5412,7 +5714,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
@@ -5557,6 +5859,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AG33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AH33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -5570,7 +5882,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>6</v>
@@ -5659,6 +5971,12 @@
       <c r="AF34" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AG34" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH34" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -5672,7 +5990,7 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -5817,6 +6135,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AG35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AH35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -5830,7 +6158,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
@@ -5975,6 +6303,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AG36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AH36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -6133,6 +6471,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -6291,6 +6639,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -6449,6 +6807,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -6603,6 +6971,16 @@
         </is>
       </c>
       <c r="AF40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AG40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH40" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -6640,7 +7018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF15"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6675,6 +7053,8 @@
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
     <col width="6" customWidth="1" min="32" max="32"/>
+    <col width="6" customWidth="1" min="33" max="33"/>
+    <col width="6" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6838,6 +7218,16 @@
           <t>08/25 09:00</t>
         </is>
       </c>
+      <c r="AG1" s="10" t="inlineStr">
+        <is>
+          <t>08/27 09:00</t>
+        </is>
+      </c>
+      <c r="AH1" s="10" t="inlineStr">
+        <is>
+          <t>08/31 16:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -6982,6 +7372,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -6996,7 +7396,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>高速道路 86、直轄国道 58</t>
+          <t>高速道路 92、直轄国道 62</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -7086,6 +7486,12 @@
       <c r="AF3" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AG3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH3" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -7100,7 +7506,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>高速道路 174、有料道路 13、一般国道 7</t>
+          <t>高速道路 182、有料道路 15、一般国道 7</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -7190,6 +7596,12 @@
       <c r="AF4" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AG4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -7340,6 +7752,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AG5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AH5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -7354,7 +7776,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>都道府県道 753、補助国道 97、市区町村道 57、国道445号 1</t>
+          <t>都道府県道 807、補助国道 107、市区町村道 61、国道445号 1</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -7442,6 +7864,12 @@
         <v>34</v>
       </c>
       <c r="AF6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH6" s="14" t="n">
         <v>34</v>
       </c>
     </row>
@@ -7569,6 +7997,14 @@
         <f>SUM(AF2:AF6)</f>
         <v/>
       </c>
+      <c r="AG7" s="12">
+        <f>SUM(AG2:AG6)</f>
+        <v/>
+      </c>
+      <c r="AH7" s="12">
+        <f>SUM(AH2:AH6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -7719,6 +8155,16 @@
         </is>
       </c>
       <c r="AF8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AG8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AH8" s="14" t="inlineStr">
         <is>
           <t>線</t>
         </is>

--- a/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
+++ b/data/mlit_r8kumamoto_map/通れる道マップ_データ一覧.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1168,11 +1168,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2608170900data.zip</t>
+          <t>2608150900data.zip</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46251.375</v>
+        <v>46249.375</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -1194,11 +1194,11 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2608180900data.zip</t>
+          <t>2608160900data.zip</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46252.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -1220,11 +1220,11 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2608190900data.zip</t>
+          <t>2608170900data.zip</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46253.375</v>
+        <v>46251.375</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -1246,11 +1246,11 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2608200900data.zip</t>
+          <t>2608180900data.zip</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46254.375</v>
+        <v>46252.375</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -1272,11 +1272,11 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2608210900data.zip</t>
+          <t>2608190900data.zip</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46255.375</v>
+        <v>46253.375</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -1298,11 +1298,11 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2608230900data.zip</t>
+          <t>2608200900data.zip</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46257.375</v>
+        <v>46254.375</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -1324,11 +1324,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2608250900data.zip</t>
+          <t>2608210900data.zip</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46259.375</v>
+        <v>46255.375</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -1350,11 +1350,11 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2608270900data.zip</t>
+          <t>2608230900data.zip</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46261.375</v>
+        <v>46257.375</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -1366,79 +1366,131 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>2608250900data.zip</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46259.375</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2608270900data.zip</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46261.375</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>2608311600data.zip</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B35" s="3" t="n">
         <v>46265.66666666666</v>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>〇の数</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>全32ファイル</t>
-        </is>
-      </c>
-      <c r="C34" s="6">
-        <f>COUNTIF(C2:C33,"〇")</f>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>全34ファイル</t>
+        </is>
+      </c>
+      <c r="C36" s="6">
+        <f>COUNTIF(C2:C35,"〇")</f>
         <v/>
       </c>
-      <c r="D34" s="6">
-        <f>COUNTIF(D2:D33,"〇")</f>
+      <c r="D36" s="6">
+        <f>COUNTIF(D2:D35,"〇")</f>
         <v/>
       </c>
-      <c r="E34" s="6">
-        <f>COUNTIF(E2:E33,"〇")</f>
+      <c r="E36" s="6">
+        <f>COUNTIF(E2:E35,"〇")</f>
         <v/>
       </c>
-      <c r="F34" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
-        </is>
-      </c>
+      <c r="F36" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+          <t>出典: 国土交通省「通れる道マップ」（https://www.mlit.go.jp/road/saigai/r8kumamoto/index.html）からダウンロードしたZIP。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>情報の日時および時刻: ファイル名の YYMMDDhhmm から読み取り（例 2608071600 → 2026/08/07 16:00）。260729data.zip だけ時刻が無く、配布元の notice.txt の記載（as of 2026/07/29 8:00）に従った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>〇の判定: ZIP内のGeoJSONのファイル名で判定（dourokisei＝道路規制情報、ETC2.0_speed_data＝ETC2.0速度情報、tukoujisseki＝通行実績情報）。連番で分割されているものも1件として〇にし、分割数は備考に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>作成: scripts/build_mlit_map_index.py</t>
         </is>
@@ -1455,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH44"/>
+  <dimension ref="A1:AJ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1492,6 +1544,8 @@
     <col width="6" customWidth="1" min="32" max="32"/>
     <col width="6" customWidth="1" min="33" max="33"/>
     <col width="6" customWidth="1" min="34" max="34"/>
+    <col width="6" customWidth="1" min="35" max="35"/>
+    <col width="6" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1622,45 +1676,55 @@
       </c>
       <c r="Z1" s="10" t="inlineStr">
         <is>
+          <t>08/15 09:00</t>
+        </is>
+      </c>
+      <c r="AA1" s="10" t="inlineStr">
+        <is>
+          <t>08/16 09:00</t>
+        </is>
+      </c>
+      <c r="AB1" s="10" t="inlineStr">
+        <is>
           <t>08/17 09:00</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AC1" s="10" t="inlineStr">
         <is>
           <t>08/18 09:00</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AD1" s="10" t="inlineStr">
         <is>
           <t>08/19 09:00</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AE1" s="10" t="inlineStr">
         <is>
           <t>08/20 09:00</t>
         </is>
       </c>
-      <c r="AD1" s="10" t="inlineStr">
+      <c r="AF1" s="10" t="inlineStr">
         <is>
           <t>08/21 09:00</t>
         </is>
       </c>
-      <c r="AE1" s="10" t="inlineStr">
+      <c r="AG1" s="10" t="inlineStr">
         <is>
           <t>08/23 09:00</t>
         </is>
       </c>
-      <c r="AF1" s="10" t="inlineStr">
+      <c r="AH1" s="10" t="inlineStr">
         <is>
           <t>08/25 09:00</t>
         </is>
       </c>
-      <c r="AG1" s="10" t="inlineStr">
+      <c r="AI1" s="10" t="inlineStr">
         <is>
           <t>08/27 09:00</t>
         </is>
       </c>
-      <c r="AH1" s="10" t="inlineStr">
+      <c r="AJ1" s="10" t="inlineStr">
         <is>
           <t>08/31 16:00</t>
         </is>
@@ -1674,7 +1738,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>29</v>
@@ -1743,7 +1807,7 @@
         <v>57</v>
       </c>
       <c r="Z2" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA2" s="12" t="n">
         <v>46</v>
@@ -1752,7 +1816,7 @@
         <v>44</v>
       </c>
       <c r="AC2" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AD2" s="12" t="n">
         <v>44</v>
@@ -1769,6 +1833,12 @@
       <c r="AH2" s="12" t="n">
         <v>44</v>
       </c>
+      <c r="AI2" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ2" s="12" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1782,7 +1852,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>10</v>
@@ -1851,7 +1921,7 @@
         <v>24</v>
       </c>
       <c r="Z3" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA3" s="15" t="n">
         <v>13</v>
@@ -1860,7 +1930,7 @@
         <v>11</v>
       </c>
       <c r="AC3" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD3" s="15" t="n">
         <v>11</v>
@@ -1877,6 +1947,12 @@
       <c r="AH3" s="15" t="n">
         <v>11</v>
       </c>
+      <c r="AI3" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ3" s="15" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1890,7 +1966,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>6</v>
@@ -1985,6 +2061,12 @@
       <c r="AH4" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AI4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1998,7 +2080,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>23</v>
@@ -2093,6 +2175,12 @@
       <c r="AH5" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AI5" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AJ5" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -2106,7 +2194,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>23</v>
@@ -2201,6 +2289,12 @@
       <c r="AH6" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AI6" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ6" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -2214,7 +2308,7 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>23</v>
@@ -2309,6 +2403,12 @@
       <c r="AH7" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AI7" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AJ7" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -2322,7 +2422,7 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>19</v>
@@ -2417,6 +2517,12 @@
       <c r="AH8" s="15" t="n">
         <v>34</v>
       </c>
+      <c r="AI8" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ8" s="15" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2430,7 +2536,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>23</v>
@@ -2525,6 +2631,12 @@
       <c r="AH9" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AI9" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AJ9" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2538,7 +2650,7 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>6</v>
@@ -2633,6 +2745,12 @@
       <c r="AH10" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2646,7 +2764,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>23</v>
@@ -2741,6 +2859,12 @@
       <c r="AH11" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AI11" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AJ11" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2754,7 +2878,7 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>23</v>
@@ -2849,6 +2973,12 @@
       <c r="AH12" s="15" t="n">
         <v>38</v>
       </c>
+      <c r="AI12" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ12" s="15" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2862,7 +2992,7 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>6</v>
@@ -2957,6 +3087,12 @@
       <c r="AH13" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AI13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2970,7 +3106,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>4</v>
@@ -3065,6 +3201,12 @@
       <c r="AH14" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AI14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ14" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -3078,7 +3220,7 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>4</v>
@@ -3173,6 +3315,12 @@
       <c r="AH15" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="AI15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -3186,7 +3334,7 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
@@ -3284,10 +3432,8 @@
       <c r="Y16" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="Z16" s="14" t="inlineStr">
-        <is>
-          <t>全</t>
-        </is>
+      <c r="Z16" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="AA16" s="15" t="n">
         <v>44</v>
@@ -3297,10 +3443,8 @@
           <t>全</t>
         </is>
       </c>
-      <c r="AC16" s="14" t="inlineStr">
-        <is>
-          <t>全</t>
-        </is>
+      <c r="AC16" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="AD16" s="14" t="inlineStr">
         <is>
@@ -3323,6 +3467,16 @@
         </is>
       </c>
       <c r="AH16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AI16" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AJ16" s="14" t="inlineStr">
         <is>
           <t>全</t>
         </is>
@@ -3340,7 +3494,7 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
@@ -3438,10 +3592,8 @@
       <c r="Y17" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="Z17" s="14" t="inlineStr">
-        <is>
-          <t>全</t>
-        </is>
+      <c r="Z17" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="AA17" s="15" t="n">
         <v>44</v>
@@ -3451,10 +3603,8 @@
           <t>全</t>
         </is>
       </c>
-      <c r="AC17" s="14" t="inlineStr">
-        <is>
-          <t>全</t>
-        </is>
+      <c r="AC17" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="AD17" s="14" t="inlineStr">
         <is>
@@ -3477,6 +3627,16 @@
         </is>
       </c>
       <c r="AH17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AI17" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AJ17" s="14" t="inlineStr">
         <is>
           <t>全</t>
         </is>
@@ -3494,7 +3654,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>23</v>
@@ -3589,6 +3749,12 @@
       <c r="AH18" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AI18" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AJ18" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -3602,7 +3768,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>23</v>
@@ -3697,6 +3863,12 @@
       <c r="AH19" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="AI19" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="AJ19" s="15" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3710,7 +3882,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
@@ -3812,10 +3984,8 @@
       <c r="Y20" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="Z20" s="14" t="inlineStr">
-        <is>
-          <t>全</t>
-        </is>
+      <c r="Z20" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="AA20" s="15" t="n">
         <v>44</v>
@@ -3825,10 +3995,8 @@
           <t>全</t>
         </is>
       </c>
-      <c r="AC20" s="14" t="inlineStr">
-        <is>
-          <t>全</t>
-        </is>
+      <c r="AC20" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="AD20" s="14" t="inlineStr">
         <is>
@@ -3851,6 +4019,16 @@
         </is>
       </c>
       <c r="AH20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AI20" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AJ20" s="14" t="inlineStr">
         <is>
           <t>全</t>
         </is>
@@ -3868,7 +4046,7 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -3970,10 +4148,8 @@
       <c r="Y21" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="Z21" s="14" t="inlineStr">
-        <is>
-          <t>全</t>
-        </is>
+      <c r="Z21" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="AA21" s="15" t="n">
         <v>44</v>
@@ -3983,10 +4159,8 @@
           <t>全</t>
         </is>
       </c>
-      <c r="AC21" s="14" t="inlineStr">
-        <is>
-          <t>全</t>
-        </is>
+      <c r="AC21" s="15" t="n">
+        <v>44</v>
       </c>
       <c r="AD21" s="14" t="inlineStr">
         <is>
@@ -4009,6 +4183,16 @@
         </is>
       </c>
       <c r="AH21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AI21" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AJ21" s="14" t="inlineStr">
         <is>
           <t>全</t>
         </is>
@@ -4165,6 +4349,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ22" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -4317,6 +4511,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ23" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -4469,6 +4673,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ24" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -4621,6 +4835,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ25" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -4773,6 +4997,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ26" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -4925,6 +5159,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ27" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -5077,6 +5321,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ28" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -5229,6 +5483,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ29" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -5381,6 +5645,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ30" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -5533,6 +5807,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ31" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -5701,6 +5985,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ32" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -5714,7 +6008,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
@@ -5869,6 +6163,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AI33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AJ33" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -5882,7 +6186,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>6</v>
@@ -5951,7 +6255,7 @@
         <v>18</v>
       </c>
       <c r="Z34" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA34" s="15" t="n">
         <v>7</v>
@@ -5960,7 +6264,7 @@
         <v>5</v>
       </c>
       <c r="AC34" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD34" s="15" t="n">
         <v>5</v>
@@ -5975,6 +6279,12 @@
         <v>5</v>
       </c>
       <c r="AH34" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI34" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ34" s="15" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5990,7 +6300,7 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -6145,6 +6455,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AI35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AJ35" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -6158,7 +6478,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
@@ -6313,6 +6633,16 @@
           <t>全</t>
         </is>
       </c>
+      <c r="AI36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="AJ36" s="14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -6481,6 +6811,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ37" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -6649,6 +6989,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ38" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -6817,6 +7167,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ39" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -6981,6 +7341,16 @@
         </is>
       </c>
       <c r="AH40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AI40" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ40" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -7018,7 +7388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH15"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7055,6 +7425,8 @@
     <col width="6" customWidth="1" min="32" max="32"/>
     <col width="6" customWidth="1" min="33" max="33"/>
     <col width="6" customWidth="1" min="34" max="34"/>
+    <col width="6" customWidth="1" min="35" max="35"/>
+    <col width="6" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7185,45 +7557,55 @@
       </c>
       <c r="Z1" s="10" t="inlineStr">
         <is>
+          <t>08/15 09:00</t>
+        </is>
+      </c>
+      <c r="AA1" s="10" t="inlineStr">
+        <is>
+          <t>08/16 09:00</t>
+        </is>
+      </c>
+      <c r="AB1" s="10" t="inlineStr">
+        <is>
           <t>08/17 09:00</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AC1" s="10" t="inlineStr">
         <is>
           <t>08/18 09:00</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AD1" s="10" t="inlineStr">
         <is>
           <t>08/19 09:00</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AE1" s="10" t="inlineStr">
         <is>
           <t>08/20 09:00</t>
         </is>
       </c>
-      <c r="AD1" s="10" t="inlineStr">
+      <c r="AF1" s="10" t="inlineStr">
         <is>
           <t>08/21 09:00</t>
         </is>
       </c>
-      <c r="AE1" s="10" t="inlineStr">
+      <c r="AG1" s="10" t="inlineStr">
         <is>
           <t>08/23 09:00</t>
         </is>
       </c>
-      <c r="AF1" s="10" t="inlineStr">
+      <c r="AH1" s="10" t="inlineStr">
         <is>
           <t>08/25 09:00</t>
         </is>
       </c>
-      <c r="AG1" s="10" t="inlineStr">
+      <c r="AI1" s="10" t="inlineStr">
         <is>
           <t>08/27 09:00</t>
         </is>
       </c>
-      <c r="AH1" s="10" t="inlineStr">
+      <c r="AJ1" s="10" t="inlineStr">
         <is>
           <t>08/31 16:00</t>
         </is>
@@ -7382,6 +7764,16 @@
           <t>－</t>
         </is>
       </c>
+      <c r="AI2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ2" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -7396,7 +7788,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>高速道路 92、直轄国道 62</t>
+          <t>高速道路 98、直轄国道 66</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -7492,6 +7884,12 @@
       <c r="AH3" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AI3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ3" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -7506,7 +7904,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>高速道路 182、有料道路 15、一般国道 7</t>
+          <t>高速道路 190、有料道路 17、一般国道 7</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -7602,6 +8000,12 @@
       <c r="AH4" s="14" t="n">
         <v>5</v>
       </c>
+      <c r="AI4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" s="14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -7616,7 +8020,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>(値なし) 56</t>
+          <t>(値なし) 60</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
@@ -7719,10 +8123,8 @@
       <c r="Y5" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="Z5" s="16" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
+      <c r="Z5" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="AA5" s="14" t="n">
         <v>2</v>
@@ -7732,10 +8134,8 @@
           <t>－</t>
         </is>
       </c>
-      <c r="AC5" s="16" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
+      <c r="AC5" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="AD5" s="16" t="inlineStr">
         <is>
@@ -7758,6 +8158,16 @@
         </is>
       </c>
       <c r="AH5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AI5" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="AJ5" s="16" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -7776,7 +8186,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>都道府県道 807、補助国道 107、市区町村道 61、国道445号 1</t>
+          <t>都道府県道 861、補助国道 117、市区町村道 65、国道445号 1</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -7870,6 +8280,12 @@
         <v>34</v>
       </c>
       <c r="AH6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI6" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ6" s="14" t="n">
         <v>34</v>
       </c>
     </row>
@@ -8005,6 +8421,14 @@
         <f>SUM(AH2:AH6)</f>
         <v/>
       </c>
+      <c r="AI7" s="12">
+        <f>SUM(AI2:AI6)</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="12">
+        <f>SUM(AJ2:AJ6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -8165,6 +8589,16 @@
         </is>
       </c>
       <c r="AH8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AI8" s="14" t="inlineStr">
+        <is>
+          <t>線</t>
+        </is>
+      </c>
+      <c r="AJ8" s="14" t="inlineStr">
         <is>
           <t>線</t>
         </is>
